--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2024_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2024_aysen.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:07</t>
+    <t xml:space="preserve">2026-09-09 22:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2024_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2024_aysen.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:04</t>
+    <t xml:space="preserve">2026-09-17 13:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -955,26 +955,26 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>409295.44</v>
+        <v>466621.78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>362494.78</v>
+        <v>409295.44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>466621.78</v>
+        <v>362494.78</v>
       </c>
     </row>
     <row r="5">
@@ -1015,101 +1015,101 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>352166.28</v>
+        <v>399113.84</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>393130.56</v>
+        <v>439330.41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>409295.44</v>
+        <v>466621.78</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>299927.28</v>
+        <v>352166.28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>333510.84</v>
+        <v>393130.56</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>362494.78</v>
+        <v>409295.44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>399113.84</v>
+        <v>299927.28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>439330.41</v>
+        <v>333510.84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>466621.78</v>
+        <v>362494.78</v>
       </c>
     </row>
     <row r="11">

--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2024_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2024_aysen.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:36</t>
+    <t xml:space="preserve">2026-09-25 21:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -527,7 +527,7 @@
         <v>248417.2</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>29137.99</v>
+        <v>29137.98</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>11.73</v>
@@ -734,7 +734,7 @@
         <v>381488.06</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>17053.35</v>
+        <v>17053.34</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>4.47</v>
@@ -780,7 +780,7 @@
         <v>405879.59</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>25036.57</v>
+        <v>25036.56</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>6.17</v>
@@ -849,7 +849,7 @@
         <v>439330.41</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>27291.37</v>
+        <v>27291.38</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>6.21</v>

--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2024_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2024_aysen.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:36</t>
+    <t xml:space="preserve">2026-10-05 07:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
